--- a/Employee_Reports_wi48/Ericson Murcillos Victorino Q0068.xlsx
+++ b/Employee_Reports_wi48/Ericson Murcillos Victorino Q0068.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-215</v>
+        <v>-218</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -664,11 +664,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-349</v>
+        <v>-352</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -738,11 +738,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
